--- a/поступенчатый_расчет_ступеней.xlsx
+++ b/поступенчатый_расчет_ступеней.xlsx
@@ -713,10 +713,10 @@
         <v>0.7</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6716666666666666</v>
+        <v>0.6721666666666666</v>
       </c>
       <c r="C2" t="n">
-        <v>100209.0768728753</v>
+        <v>100218.4308867928</v>
       </c>
       <c r="D2" t="n">
         <v>288</v>
@@ -725,40 +725,40 @@
         <v>0.4</v>
       </c>
       <c r="F2" t="n">
-        <v>299.2797740508382</v>
+        <v>297.6484864069328</v>
       </c>
       <c r="G2" t="n">
-        <v>11942.72788515835</v>
+        <v>11812.889983149</v>
       </c>
       <c r="H2" t="n">
-        <v>11823.30060630677</v>
+        <v>11694.76108331751</v>
       </c>
       <c r="I2" t="n">
-        <v>9110.682164044398</v>
+        <v>9011.633448421931</v>
       </c>
       <c r="J2" t="n">
-        <v>11.75278390288943</v>
+        <v>11.62501101721422</v>
       </c>
       <c r="K2" t="n">
-        <v>299.7527839028894</v>
+        <v>299.6250110172142</v>
       </c>
       <c r="L2" t="n">
-        <v>299.7527839028894</v>
+        <v>299.6250110172142</v>
       </c>
       <c r="M2" t="n">
-        <v>1.114454146199309</v>
+        <v>1.113161849170437</v>
       </c>
       <c r="N2" t="n">
-        <v>111678.4212077812</v>
+        <v>111559.3338469019</v>
       </c>
       <c r="O2" t="n">
-        <v>111678.4212077812</v>
+        <v>111559.3338469019</v>
       </c>
       <c r="P2" t="n">
         <v>310.7513475433373</v>
       </c>
       <c r="Q2" t="n">
-        <v>317.0285609257293</v>
+        <v>316.9609852869465</v>
       </c>
       <c r="R2" t="n">
         <v>0.7615773105863909</v>
@@ -770,2230 +770,2230 @@
         <v>1.174080662328612</v>
       </c>
       <c r="U2" t="n">
-        <v>209.4958418355867</v>
+        <v>208.3539404848529</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7309264793494213</v>
+        <v>0.7269424101347626</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9132136499150542</v>
+        <v>0.9106507829657974</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2922061150544717</v>
+        <v>0.293001127744622</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6716666666666666</v>
+        <v>0.6721666666666666</v>
       </c>
       <c r="Z2" t="n">
-        <v>201.0162482374796</v>
+        <v>200.0693909465266</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6874546951071757</v>
+        <v>0.6843624155051158</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8833290106059594</v>
+        <v>0.8810437960869254</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.2765428059334065</v>
+        <v>0.2774968987469673</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.450446085074406</v>
+        <v>0.4374475173572833</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.7771446234466394</v>
+        <v>0.7732538757837157</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3018018873161736</v>
+        <v>0.2995217868300289</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.14849735436527</v>
+        <v>1.151602100275277</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.6951314545180689</v>
+        <v>0.6910439251322914</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.2748060898888096</v>
+        <v>0.2759585643602346</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1221216313801273</v>
+        <v>0.1226195266860898</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.4559687834754019</v>
+        <v>0.4425416509539824</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.7693609670165151</v>
+        <v>0.7674155931850533</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.463590209450132</v>
+        <v>0.4647653957116505</v>
       </c>
       <c r="AN2" t="n">
         <v>0.9811521435425956</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6858333333333333</v>
+        <v>0.6860833333333333</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.151408670288258</v>
+        <v>1.155345257978446</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.976393138219331</v>
+        <v>0.9753871839595102</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.1702565267456628</v>
+        <v>0.1741931144358506</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.1721042161459388</v>
+        <v>0.1762149163157664</v>
       </c>
       <c r="AT2" t="n">
-        <v>252.0588558778134</v>
+        <v>250.6849558258153</v>
       </c>
       <c r="AU2" t="n">
-        <v>205.2560450365332</v>
+        <v>204.2116657156898</v>
       </c>
       <c r="AV2" t="n">
-        <v>247.749292866803</v>
+        <v>246.6565457577842</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.91095774696431</v>
+        <v>0.9119257887245771</v>
       </c>
       <c r="AX2" t="n">
-        <v>262.3558311257213</v>
+        <v>262.6346271526782</v>
       </c>
       <c r="AY2" t="n">
-        <v>296.5938471655377</v>
+        <v>296.7513950839878</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.8498451949919646</v>
+        <v>0.8447642032310091</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.7814731018031008</v>
+        <v>0.7781921347022716</v>
       </c>
       <c r="BB2" t="n">
-        <v>299.7527839028894</v>
+        <v>299.6250110172142</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.8982166318597068</v>
+        <v>0.8990695002479203</v>
       </c>
       <c r="BD2" t="n">
-        <v>659.2066991617698</v>
+        <v>659.8326245065829</v>
       </c>
       <c r="BE2" t="n">
-        <v>470.1404111847241</v>
+        <v>470.3635604477214</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.5269687246039761</v>
+        <v>0.5243955240133847</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.6716666666666666</v>
+        <v>0.6721666666666666</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6433333333333333</v>
+        <v>0.6443333333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>246120.9412493957</v>
+        <v>246143.2575260414</v>
       </c>
       <c r="D3" t="n">
         <v>325.1588448135019</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4420130879603985</v>
+        <v>0.442011222595712</v>
       </c>
       <c r="F3" t="n">
-        <v>299.1162677083258</v>
+        <v>297.4822304909237</v>
       </c>
       <c r="G3" t="n">
-        <v>14402.60321610342</v>
+        <v>14204.40481079624</v>
       </c>
       <c r="H3" t="n">
-        <v>14114.55115178135</v>
+        <v>13920.31671458031</v>
       </c>
       <c r="I3" t="n">
-        <v>11253.29696793078</v>
+        <v>11092.2245090369</v>
       </c>
       <c r="J3" t="n">
-        <v>13.9748031205756</v>
+        <v>13.78249179661417</v>
       </c>
       <c r="K3" t="n">
-        <v>339.1336479340775</v>
+        <v>338.9413366101161</v>
       </c>
       <c r="L3" t="n">
-        <v>339.1336479340775</v>
+        <v>338.9413366101161</v>
       </c>
       <c r="M3" t="n">
-        <v>1.125156158329076</v>
+        <v>1.123289797933352</v>
       </c>
       <c r="N3" t="n">
-        <v>276924.4927405063</v>
+        <v>276490.2100090841</v>
       </c>
       <c r="O3" t="n">
-        <v>276924.4927405063</v>
+        <v>276490.2100090841</v>
       </c>
       <c r="P3" t="n">
         <v>330.1904914832758</v>
       </c>
       <c r="Q3" t="n">
-        <v>337.2113760718879</v>
+        <v>337.1157518796354</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7731027001402487</v>
+        <v>0.7731021668901711</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2824410389818248</v>
+        <v>0.2827423012403118</v>
       </c>
       <c r="T3" t="n">
-        <v>1.172736799837135</v>
+        <v>1.172621754008351</v>
       </c>
       <c r="U3" t="n">
-        <v>200.9064264774255</v>
+        <v>199.9576392616492</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6600632225500643</v>
+        <v>0.6569778396427248</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8623629605972387</v>
+        <v>0.8598998937581854</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1339450277165203</v>
+        <v>0.1343230154919619</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6433333333333333</v>
+        <v>0.6443333333333333</v>
       </c>
       <c r="Z3" t="n">
-        <v>192.4314655590229</v>
+        <v>191.6777171796518</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6190562878693208</v>
+        <v>0.6168362177197966</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8279833363157526</v>
+        <v>0.826021917245764</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1266251427709135</v>
+        <v>0.1270952810443449</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.7968812041255451</v>
+        <v>0.7934973681907749</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.9077445768780409</v>
+        <v>0.9062782802759544</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3630618950569947</v>
+        <v>0.3624287257396914</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.057006493208234</v>
+        <v>1.058417211055684</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.6552567399148586</v>
+        <v>0.6523565444133773</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1221216313801273</v>
+        <v>0.1226195266860898</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.08527959127161663</v>
+        <v>0.08562308417067097</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8049847412858127</v>
+        <v>0.8016736509327737</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8404236385091448</v>
+        <v>0.8396902235830628</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.45135790774494</v>
+        <v>0.4514739650918165</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9398835745940116</v>
+        <v>0.9405309585052282</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.6575</v>
+        <v>0.65825</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.036476233073305</v>
+        <v>1.037932668457427</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9692047196450475</v>
+        <v>0.9696166277691937</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.09659265847929321</v>
+        <v>0.09740170995219888</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.08780177356318641</v>
+        <v>0.08880058328649054</v>
       </c>
       <c r="AT3" t="n">
-        <v>248.8037853576839</v>
+        <v>247.5117991946897</v>
       </c>
       <c r="AU3" t="n">
-        <v>196.6689460182242</v>
+        <v>195.8176782206505</v>
       </c>
       <c r="AV3" t="n">
-        <v>238.5497169285235</v>
+        <v>237.4500487211659</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.9273860903728041</v>
+        <v>0.9280633530363964</v>
       </c>
       <c r="AX3" t="n">
-        <v>301.5477898417308</v>
+        <v>301.7680077870598</v>
       </c>
       <c r="AY3" t="n">
-        <v>317.9763732322456</v>
+        <v>318.0924598461918</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.7824599759679661</v>
+        <v>0.7781127516017506</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.7074189480418615</v>
+        <v>0.7043576201860351</v>
       </c>
       <c r="BB3" t="n">
-        <v>339.1336479340775</v>
+        <v>338.9413366101161</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.916593071991891</v>
+        <v>0.9173133904809776</v>
       </c>
       <c r="BD3" t="n">
-        <v>672.6932813649961</v>
+        <v>673.2219275252803</v>
       </c>
       <c r="BE3" t="n">
-        <v>474.9253175412774</v>
+        <v>475.1118945040489</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.5022889033659281</v>
+        <v>0.4997771082305378</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.6433333333333333</v>
+        <v>0.6443333333333333</v>
       </c>
       <c r="B4" t="n">
-        <v>0.615</v>
+        <v>0.6164999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>392032.805625916</v>
+        <v>392068.0841652899</v>
       </c>
       <c r="D4" t="n">
         <v>362.3176896270037</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4840261759207969</v>
+        <v>0.484022445191424</v>
       </c>
       <c r="F4" t="n">
-        <v>298.9527613658134</v>
+        <v>297.3159745749147</v>
       </c>
       <c r="G4" t="n">
-        <v>16654.26948495627</v>
+        <v>16396.08656269553</v>
       </c>
       <c r="H4" t="n">
-        <v>16154.64140040758</v>
+        <v>15904.20396581466</v>
       </c>
       <c r="I4" t="n">
-        <v>13263.05712505622</v>
+        <v>13044.98382643853</v>
       </c>
       <c r="J4" t="n">
-        <v>15.90840909164649</v>
+        <v>15.66178887504014</v>
       </c>
       <c r="K4" t="n">
-        <v>378.2260987186502</v>
+        <v>377.9794785020439</v>
       </c>
       <c r="L4" t="n">
-        <v>378.2260987186502</v>
+        <v>377.9794785020439</v>
       </c>
       <c r="M4" t="n">
-        <v>1.131956806735649</v>
+        <v>1.129691903074519</v>
       </c>
       <c r="N4" t="n">
-        <v>443764.2027919294</v>
+        <v>442916.140135467</v>
       </c>
       <c r="O4" t="n">
-        <v>443764.2027919294</v>
+        <v>442916.140135467</v>
       </c>
       <c r="P4" t="n">
         <v>348.5471579742609</v>
       </c>
       <c r="Q4" t="n">
-        <v>356.1168500652046</v>
+        <v>356.0007291309041</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7855830124743375</v>
+        <v>0.7855818631591125</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2741877701129128</v>
+        <v>0.2747365065866861</v>
       </c>
       <c r="T4" t="n">
-        <v>1.167910887156486</v>
+        <v>1.167749955007179</v>
       </c>
       <c r="U4" t="n">
-        <v>192.3262764786733</v>
+        <v>191.5705929511034</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5998195750552469</v>
+        <v>0.5975037691519378</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8106531160561622</v>
+        <v>0.8085161418424881</v>
       </c>
       <c r="X4" t="n">
-        <v>0.09462198677788529</v>
+        <v>0.09487005204389491</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.615</v>
+        <v>0.6164999999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>183.8559482399753</v>
+        <v>183.2952983254349</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5612142875647176</v>
+        <v>0.5597238197893952</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7736370102233894</v>
+        <v>0.7721493996791461</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.08949339903639882</v>
+        <v>0.08981436860973413</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.8614215164036316</v>
+        <v>0.8592301749844373</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.9365342429610974</v>
+        <v>0.9355453231892149</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.366809882736139</v>
+        <v>0.3666594076777121</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.032999445544482</v>
+        <v>1.03425081694109</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.6011367121652327</v>
+        <v>0.59905244559614</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.08527959127161663</v>
+        <v>0.08562308417067097</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.06940690509281372</v>
+        <v>0.0696675211969156</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8684427306837406</v>
+        <v>0.8663083189502597</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.8610586277177175</v>
+        <v>0.8605635931741638</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.466569176740235</v>
+        <v>0.4663349114295255</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.8991637652436869</v>
+        <v>0.900444024849219</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.6291666666666667</v>
+        <v>0.6304166666666666</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.010757875954717</v>
+        <v>1.011948080468751</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9327142827339665</v>
+        <v>0.9339037741484145</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.1115941107110298</v>
+        <v>0.1115040556195322</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.1002851628105159</v>
+        <v>0.1003470427926759</v>
       </c>
       <c r="AT4" t="n">
-        <v>245.6880428177402</v>
+        <v>244.4740913624744</v>
       </c>
       <c r="AU4" t="n">
-        <v>188.0911123593243</v>
+        <v>187.4329456382691</v>
       </c>
       <c r="AV4" t="n">
-        <v>234.1656144163051</v>
+        <v>233.140738673485</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.9400360795634238</v>
+        <v>0.940498207641538</v>
       </c>
       <c r="AX4" t="n">
-        <v>340.591700513446</v>
+        <v>340.7591376910201</v>
       </c>
       <c r="AY4" t="n">
-        <v>337.9354926345536</v>
+        <v>338.0185481120807</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.7270264537836794</v>
+        <v>0.7232564388194795</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.6575527509395571</v>
+        <v>0.6548883740846425</v>
       </c>
       <c r="BB4" t="n">
-        <v>378.2260987186502</v>
+        <v>377.9794785020439</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.9279373966219702</v>
+        <v>0.9285202029147955</v>
       </c>
       <c r="BD4" t="n">
-        <v>681.0189508397762</v>
+        <v>681.446675955207</v>
       </c>
       <c r="BE4" t="n">
-        <v>477.8552649250366</v>
+        <v>478.0053037862455</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.4900346016968962</v>
+        <v>0.4877367192932673</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.615</v>
+        <v>0.6164999999999999</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.5886666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>537944.6700024364</v>
+        <v>537992.9108045385</v>
       </c>
       <c r="D5" t="n">
         <v>399.4765344405056</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5260392638811953</v>
+        <v>0.5260336677871359</v>
       </c>
       <c r="F5" t="n">
-        <v>298.7892550233011</v>
+        <v>297.1497186589057</v>
       </c>
       <c r="G5" t="n">
-        <v>18747.29322238706</v>
+        <v>18434.80345716985</v>
       </c>
       <c r="H5" t="n">
-        <v>17997.40149349157</v>
+        <v>17697.41131888305</v>
       </c>
       <c r="I5" t="n">
-        <v>15144.67185448543</v>
+        <v>14874.55351718711</v>
       </c>
       <c r="J5" t="n">
-        <v>17.69728869929402</v>
+        <v>17.40230096293005</v>
       </c>
       <c r="K5" t="n">
-        <v>417.1738231397996</v>
+        <v>416.8788354034356</v>
       </c>
       <c r="L5" t="n">
-        <v>417.1738231397996</v>
+        <v>416.8788354034356</v>
       </c>
       <c r="M5" t="n">
-        <v>1.136670815210054</v>
+        <v>1.134122701316078</v>
       </c>
       <c r="N5" t="n">
-        <v>611466.0065895729</v>
+        <v>610149.9732905431</v>
       </c>
       <c r="O5" t="n">
-        <v>611466.0065895729</v>
+        <v>610149.9732905431</v>
       </c>
       <c r="P5" t="n">
         <v>365.9842646862041</v>
       </c>
       <c r="Q5" t="n">
-        <v>374.0031856799816</v>
+        <v>373.8709316204885</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7989734999186987</v>
+        <v>0.7989716577093292</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2680713532032626</v>
+        <v>0.2688306900680616</v>
       </c>
       <c r="T5" t="n">
-        <v>1.15973939006482</v>
+        <v>1.159595588584208</v>
       </c>
       <c r="U5" t="n">
-        <v>183.7553918393301</v>
+        <v>183.1928015532153</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5477103116172261</v>
+        <v>0.546067661412585</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7600035150396606</v>
+        <v>0.7583214161141775</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07750449130671022</v>
+        <v>0.07767431522539926</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.5886666666666667</v>
       </c>
       <c r="Z5" t="n">
-        <v>175.2896962803366</v>
+        <v>174.9221343838758</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5112747284910509</v>
+        <v>0.5104151246580626</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.721512486287147</v>
+        <v>0.7205750330952487</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.07339674468734096</v>
+        <v>0.07362931958543495</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.8879434224006204</v>
+        <v>0.8862508256135369</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.9486684642429083</v>
+        <v>0.9478885488528848</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3617824914834868</v>
+        <v>0.3619351754531361</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.018206155431839</v>
+        <v>1.019537248096724</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.5506376385743473</v>
+        <v>0.5492270447061419</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.06940690509281372</v>
+        <v>0.0696675211969156</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.06113456393285029</v>
+        <v>0.06133289317746405</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8943957234345412</v>
+        <v>0.8927403889669466</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.8738209820808035</v>
+        <v>0.8734301032811069</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.4854275131566459</v>
+        <v>0.4849473428323655</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8586569080400985</v>
+        <v>0.8605710404830875</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.6008333333333333</v>
+        <v>0.6025833333333332</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9969386506490047</v>
+        <v>0.9981591509554445</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.8912424767696401</v>
+        <v>0.8931472086948627</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.1382817426089061</v>
+        <v>0.137588110472357</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.126963678662199</v>
+        <v>0.1263900394018608</v>
       </c>
       <c r="AT5" t="n">
-        <v>242.7526333885028</v>
+        <v>241.6106246066719</v>
       </c>
       <c r="AU5" t="n">
-        <v>179.5225440598334</v>
+        <v>179.0574679685456</v>
       </c>
       <c r="AV5" t="n">
-        <v>230.7923259662675</v>
+        <v>229.8411485803474</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.9500022357580269</v>
+        <v>0.9503016848598984</v>
       </c>
       <c r="AX5" t="n">
-        <v>379.5036008513487</v>
+        <v>379.6232237408057</v>
       </c>
       <c r="AY5" t="n">
-        <v>356.7177558875605</v>
+        <v>356.7739717528343</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.6805173821092882</v>
+        <v>0.6772092241472559</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.6170865244012829</v>
+        <v>0.6147606811370298</v>
       </c>
       <c r="BB5" t="n">
-        <v>417.1738231397996</v>
+        <v>416.8788354034356</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.9365340369003908</v>
+        <v>0.9370115508213226</v>
       </c>
       <c r="BD5" t="n">
-        <v>687.3280779042412</v>
+        <v>687.6785283016799</v>
       </c>
       <c r="BE5" t="n">
-        <v>480.0636463233725</v>
+        <v>480.1860166014346</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.4807535995150214</v>
+        <v>0.4786502326891389</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.5886666666666667</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5583333333333333</v>
+        <v>0.5608333333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>683856.5343789568</v>
+        <v>683917.737443787</v>
       </c>
       <c r="D6" t="n">
         <v>436.6353792540075</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5680523518415938</v>
+        <v>0.5680448903828479</v>
       </c>
       <c r="F6" t="n">
-        <v>298.6257486807887</v>
+        <v>296.9834627428966</v>
       </c>
       <c r="G6" t="n">
-        <v>20715.69818169599</v>
+        <v>20352.94240210453</v>
       </c>
       <c r="H6" t="n">
-        <v>19679.91327261119</v>
+        <v>19335.29528199931</v>
       </c>
       <c r="I6" t="n">
-        <v>16894.87925955694</v>
+        <v>16578.14612092935</v>
       </c>
       <c r="J6" t="n">
-        <v>19.24881214991654</v>
+        <v>18.91174323742281</v>
       </c>
       <c r="K6" t="n">
-        <v>455.884191403924</v>
+        <v>455.5471224914303</v>
       </c>
       <c r="L6" t="n">
-        <v>455.884191403924</v>
+        <v>455.5471224914303</v>
       </c>
       <c r="M6" t="n">
-        <v>1.138845512224701</v>
+        <v>1.136122909736611</v>
       </c>
       <c r="N6" t="n">
-        <v>778806.9451830122</v>
+        <v>777014.6098851146</v>
       </c>
       <c r="O6" t="n">
-        <v>778806.9451830122</v>
+        <v>777014.6098851146</v>
       </c>
       <c r="P6" t="n">
         <v>382.6275508426814</v>
       </c>
       <c r="Q6" t="n">
-        <v>390.9705479671528</v>
+        <v>390.8259845140502</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8132292033715851</v>
+        <v>0.8132265974161389</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2637902997206379</v>
+        <v>0.2647333246898356</v>
       </c>
       <c r="T6" t="n">
-        <v>1.148239690862785</v>
+        <v>1.148177885393446</v>
       </c>
       <c r="U6" t="n">
-        <v>175.193772559396</v>
+        <v>174.8242650679852</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5020267886984568</v>
+        <v>0.5009818693570599</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7113575478666747</v>
+        <v>0.7102005621563435</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06844664808489333</v>
+        <v>0.06855392439818238</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5583333333333333</v>
+        <v>0.5608333333333333</v>
       </c>
       <c r="Z6" t="n">
-        <v>166.732709680107</v>
+        <v>166.5582253549745</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4675857106038412</v>
+        <v>0.4672821483494672</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6722207744448776</v>
+        <v>0.6718668036160703</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.06498770336807287</v>
+        <v>0.0651496406683529</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.9014884795553313</v>
+        <v>0.9000837344981281</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.9549313187935986</v>
+        <v>0.9542727387440068</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.3540069806417601</v>
+        <v>0.354396933542136</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.005721054024286</v>
+        <v>1.00724250187934</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.5049545331268156</v>
+        <v>0.5041269572133141</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.06113456393285029</v>
+        <v>0.06133289317746405</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.05652836897522951</v>
+        <v>0.05666996572855271</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.907627482630271</v>
+        <v>0.9062410936500147</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.8840802610825919</v>
+        <v>0.8837496680800728</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.5054063319661363</v>
+        <v>0.5047236044273561</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.8181543159358577</v>
+        <v>0.8207113081684391</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5725</v>
+        <v>0.57475</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.9864214910045324</v>
+        <v>0.9877978302091043</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.8475623963783884</v>
+        <v>0.8501782687194871</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.1682671750686746</v>
+        <v>0.1670865220406652</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.1581586576458981</v>
+        <v>0.1570642331598527</v>
       </c>
       <c r="AT6" t="n">
-        <v>240.0291438756836</v>
+        <v>238.9514462356655</v>
       </c>
       <c r="AU6" t="n">
-        <v>170.9632411197515</v>
+        <v>170.6912452114798</v>
       </c>
       <c r="AV6" t="n">
-        <v>228.0515140554598</v>
+        <v>227.1648772145853</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.9579948505715191</v>
+        <v>0.9581695277625843</v>
       </c>
       <c r="AX6" t="n">
-        <v>418.2944449026815</v>
+        <v>418.3707151442493</v>
       </c>
       <c r="AY6" t="n">
-        <v>374.5051767010292</v>
+        <v>374.5393180800472</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.6409234339297291</v>
+        <v>0.6379876149200346</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.5832958908061264</v>
+        <v>0.5812430243015705</v>
       </c>
       <c r="BB6" t="n">
-        <v>455.884191403924</v>
+        <v>455.5471224914303</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.9432943172947812</v>
+        <v>0.9436927577834606</v>
       </c>
       <c r="BD6" t="n">
-        <v>692.2894891786766</v>
+        <v>692.5819070988514</v>
       </c>
       <c r="BE6" t="n">
-        <v>481.7931773298687</v>
+        <v>481.8949195107216</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.4733390275871841</v>
+        <v>0.4713991951714924</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.5583333333333333</v>
+        <v>0.5608333333333333</v>
       </c>
       <c r="B7" t="n">
-        <v>0.53</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>829768.3987554772</v>
+        <v>829842.5640830356</v>
       </c>
       <c r="D7" t="n">
         <v>473.7942240675094</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6100654398019921</v>
+        <v>0.6100561129785599</v>
       </c>
       <c r="F7" t="n">
-        <v>298.4622423382763</v>
+        <v>296.8172068268876</v>
       </c>
       <c r="G7" t="n">
-        <v>22582.49104709237</v>
+        <v>22172.89458908636</v>
       </c>
       <c r="H7" t="n">
-        <v>21227.54158426683</v>
+        <v>20842.52091374118</v>
       </c>
       <c r="I7" t="n">
-        <v>18505.15677359926</v>
+        <v>18148.35300167006</v>
       </c>
       <c r="J7" t="n">
-        <v>20.63316056288989</v>
+        <v>20.25892064992346</v>
       </c>
       <c r="K7" t="n">
-        <v>494.4273846303993</v>
+        <v>494.0531447174329</v>
       </c>
       <c r="L7" t="n">
-        <v>494.4273846303993</v>
+        <v>494.0531447174329</v>
       </c>
       <c r="M7" t="n">
-        <v>1.139298819137937</v>
+        <v>1.136489207037134</v>
       </c>
       <c r="N7" t="n">
-        <v>945354.156860092</v>
+        <v>943107.117620391</v>
       </c>
       <c r="O7" t="n">
-        <v>945354.156860092</v>
+        <v>943107.117620391</v>
       </c>
       <c r="P7" t="n">
         <v>398.5764711192018</v>
       </c>
       <c r="Q7" t="n">
-        <v>407.162746412995</v>
+        <v>407.0086232793541</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8283054511594132</v>
+        <v>0.8283020164718028</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2611241497250116</v>
+        <v>0.2622273077150689</v>
       </c>
       <c r="T7" t="n">
-        <v>1.133333234410327</v>
+        <v>1.133429879937692</v>
       </c>
       <c r="U7" t="n">
-        <v>166.641418638871</v>
+        <v>166.4649834954128</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4615565545063565</v>
+        <v>0.4610470346756654</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6651615762621873</v>
+        <v>0.6645622330699885</v>
       </c>
       <c r="X7" t="n">
-        <v>0.06327405475148125</v>
+        <v>0.06332259725282313</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.53</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>158.1849884392865</v>
+        <v>158.2035712387311</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4288948764870528</v>
+        <v>0.4290882982604481</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6258871336899617</v>
+        <v>0.626124728303356</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.06029419845250476</v>
+        <v>0.06038932252172544</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.908960884951579</v>
+        <v>0.9077568679537927</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.9584008554195593</v>
+        <v>0.9578259029504064</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.3451340129398243</v>
+        <v>0.3457271323417761</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.9935806162112929</v>
+        <v>0.995375106261994</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.4636185997090251</v>
+        <v>0.4633079844547169</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.05652836897522951</v>
+        <v>0.05666996572855271</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.05400376985493811</v>
+        <v>0.05408742983334248</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.9149122358663075</v>
+        <v>0.913707240162582</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.8933531532894863</v>
+        <v>0.8930639597111045</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.5258831426787041</v>
+        <v>0.5250249073857695</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.7775370609578073</v>
+        <v>0.7807470850194044</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5441666666666667</v>
+        <v>0.5469166666666666</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.9768478355014064</v>
+        <v>0.9784670496224878</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.8024831110649353</v>
+        <v>0.8058178551378355</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.1993107745435991</v>
+        <v>0.1977199646030834</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.1910975051463576</v>
+        <v>0.1895572511241584</v>
       </c>
       <c r="AT7" t="n">
-        <v>237.5412104699469</v>
+        <v>236.5196630989821</v>
       </c>
       <c r="AU7" t="n">
-        <v>162.4132035390787</v>
+        <v>162.3342773670719</v>
       </c>
       <c r="AV7" t="n">
-        <v>225.8612779030129</v>
+        <v>225.0275748442967</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.9644942578320368</v>
+        <v>0.964572605302796</v>
       </c>
       <c r="AX7" t="n">
-        <v>456.9718085070982</v>
+        <v>457.0089290862142</v>
       </c>
       <c r="AY7" t="n">
-        <v>391.4366454388629</v>
+        <v>391.4525436404873</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.6068445896362752</v>
+        <v>0.6042103109086024</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.5547198998257968</v>
+        <v>0.5528815901520763</v>
       </c>
       <c r="BB7" t="n">
-        <v>494.4273846303993</v>
+        <v>494.0531447174329</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.9487143054562097</v>
+        <v>0.9490536578784853</v>
       </c>
       <c r="BD7" t="n">
-        <v>696.2672517569465</v>
+        <v>696.516304582519</v>
       </c>
       <c r="BE7" t="n">
-        <v>483.1753403414791</v>
+        <v>483.2617478411866</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.4674519973295571</v>
+        <v>0.4656432582333147</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.53</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5016666666666666</v>
+        <v>0.5051666666666667</v>
       </c>
       <c r="C8" t="n">
-        <v>975680.2631319974</v>
+        <v>975767.3907222842</v>
       </c>
       <c r="D8" t="n">
         <v>510.9530688810112</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6520785277623906</v>
+        <v>0.6520673355742719</v>
       </c>
       <c r="F8" t="n">
-        <v>298.2987359957639</v>
+        <v>296.6509509108786</v>
       </c>
       <c r="G8" t="n">
-        <v>24357.33346938012</v>
+        <v>23904.7446241814</v>
       </c>
       <c r="H8" t="n">
-        <v>22895.89346121731</v>
+        <v>22470.45994673052</v>
       </c>
       <c r="I8" t="n">
-        <v>20172.98184774498</v>
+        <v>19780.32064898294</v>
       </c>
       <c r="J8" t="n">
-        <v>22.09621777770937</v>
+        <v>21.68564320886978</v>
       </c>
       <c r="K8" t="n">
-        <v>533.0492866587206</v>
+        <v>532.638712089881</v>
       </c>
       <c r="L8" t="n">
-        <v>533.0492866587206</v>
+        <v>532.638712089881</v>
       </c>
       <c r="M8" t="n">
-        <v>1.139830595706935</v>
+        <v>1.136983004032705</v>
       </c>
       <c r="N8" t="n">
-        <v>1112110.215545244</v>
+        <v>1109430.939140577</v>
       </c>
       <c r="O8" t="n">
-        <v>1112110.215545244</v>
+        <v>1109430.939140577</v>
       </c>
       <c r="P8" t="n">
         <v>413.9112996715638</v>
       </c>
       <c r="Q8" t="n">
-        <v>422.7663962718289</v>
+        <v>422.6035496345684</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8441582808836169</v>
+        <v>0.8441539581506831</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2599455370180582</v>
+        <v>0.261182566675198</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11480716130118</v>
+        <v>1.115161661381325</v>
       </c>
       <c r="U8" t="n">
-        <v>158.0983300777549</v>
+        <v>158.1149568354982</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4254297694104868</v>
+        <v>0.4254005733095945</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6216207931674735</v>
+        <v>0.6215847667051542</v>
       </c>
       <c r="X8" t="n">
-        <v>0.06032905642567754</v>
+        <v>0.06031668243778929</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5016666666666666</v>
+        <v>0.5051666666666667</v>
       </c>
       <c r="Z8" t="n">
-        <v>149.6465325578749</v>
+        <v>149.8581720351455</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.3942521539117713</v>
+        <v>0.3948932314879272</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5824110292419802</v>
+        <v>0.5832318344483126</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.05769993743614724</v>
+        <v>0.05772560230189012</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.9130648975245105</v>
+        <v>0.912022337231375</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.9602971479676159</v>
+        <v>0.9597881427391327</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.3358212805680746</v>
+        <v>0.3365923757974178</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.9808960743239118</v>
+        <v>0.9830478511790475</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.4259583890287898</v>
+        <v>0.4261123821936286</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.05400376985493811</v>
+        <v>0.05408742983334248</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.05291608030369088</v>
+        <v>0.05293402055671876</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.9188804192001668</v>
+        <v>0.917816189596407</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9022277144256163</v>
+        <v>0.9019710504449079</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.5466114791716585</v>
+        <v>0.5456024418520964</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.736780855573857</v>
+        <v>0.7406496754767768</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5158333333333334</v>
+        <v>0.5190833333333333</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.9672189729071605</v>
+        <v>0.9691649048738225</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.7564370917226861</v>
+        <v>0.7604953920954729</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.2304381173333035</v>
+        <v>0.2285152293970456</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.2244589826012257</v>
+        <v>0.2225524590835746</v>
       </c>
       <c r="AT8" t="n">
-        <v>235.2978709050097</v>
+        <v>234.325080594597</v>
       </c>
       <c r="AU8" t="n">
-        <v>153.8724313178149</v>
+        <v>153.9865644353219</v>
       </c>
       <c r="AV8" t="n">
-        <v>224.1944988729534</v>
+        <v>223.4019069946754</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.96983491854989</v>
+        <v>0.9698390587046447</v>
       </c>
       <c r="AX8" t="n">
-        <v>495.5401279410319</v>
+        <v>495.5422433658094</v>
       </c>
       <c r="AY8" t="n">
-        <v>407.6206629927241</v>
+        <v>407.6215330432826</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.577247162048823</v>
+        <v>0.5748594262063079</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.5303034982203306</v>
+        <v>0.5286323486583452</v>
       </c>
       <c r="BB8" t="n">
-        <v>533.0492866587206</v>
+        <v>532.638712089881</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.9531296999625466</v>
+        <v>0.9534246399919937</v>
       </c>
       <c r="BD8" t="n">
-        <v>699.5077368857878</v>
+        <v>699.7241951836708</v>
       </c>
       <c r="BE8" t="n">
-        <v>484.2984040628305</v>
+        <v>484.3733298243048</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.4629263631516479</v>
+        <v>0.4612184305764921</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.5016666666666666</v>
+        <v>0.5051666666666667</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4733333333333333</v>
+        <v>0.4773333333333333</v>
       </c>
       <c r="C9" t="n">
-        <v>1121592.127508518</v>
+        <v>1121692.217361533</v>
       </c>
       <c r="D9" t="n">
         <v>548.1119136945131</v>
       </c>
       <c r="E9" t="n">
-        <v>0.694091615722789</v>
+        <v>0.6940785581699838</v>
       </c>
       <c r="F9" t="n">
-        <v>298.1352296532515</v>
+        <v>296.4846949948695</v>
       </c>
       <c r="G9" t="n">
-        <v>26034.87183705304</v>
+        <v>25544.60505934912</v>
       </c>
       <c r="H9" t="n">
-        <v>24472.77952682986</v>
+        <v>24011.92875578817</v>
       </c>
       <c r="I9" t="n">
-        <v>21688.3740289623</v>
+        <v>21270.26966384472</v>
       </c>
       <c r="J9" t="n">
-        <v>23.44984156300196</v>
+        <v>23.00825389809177</v>
       </c>
       <c r="K9" t="n">
-        <v>571.5617552575151</v>
+        <v>571.1201675926048</v>
       </c>
       <c r="L9" t="n">
-        <v>571.5617552575151</v>
+        <v>571.1201675926048</v>
       </c>
       <c r="M9" t="n">
-        <v>1.13911266992671</v>
+        <v>1.136307478140873</v>
       </c>
       <c r="N9" t="n">
-        <v>1277619.802935006</v>
+        <v>1274587.254760327</v>
       </c>
       <c r="O9" t="n">
-        <v>1277619.802935006</v>
+        <v>1274587.254760327</v>
       </c>
       <c r="P9" t="n">
         <v>428.6979410514707</v>
       </c>
       <c r="Q9" t="n">
-        <v>437.7723798252293</v>
+        <v>437.6032360412802</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8607447853506497</v>
+        <v>0.8607395206772266</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2602253317062639</v>
+        <v>0.2615618109547634</v>
       </c>
       <c r="T9" t="n">
-        <v>1.092283865280992</v>
+        <v>1.093031388725449</v>
       </c>
       <c r="U9" t="n">
-        <v>149.5645068760478</v>
+        <v>149.7741850882416</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3930251047657395</v>
+        <v>0.3934236537978833</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5808383070169312</v>
+        <v>0.581349371500232</v>
       </c>
       <c r="X9" t="n">
-        <v>0.05883676250242988</v>
+        <v>0.05875702662084882</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4733333333333333</v>
+        <v>0.4773333333333333</v>
       </c>
       <c r="Z9" t="n">
-        <v>141.1173420358724</v>
+        <v>141.5220277442177</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.3631409094847604</v>
+        <v>0.3641819504126783</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.5418751536373568</v>
+        <v>0.5432533028549134</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.05653729914183332</v>
+        <v>0.05648431998227224</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.9148981688173264</v>
+        <v>0.9140032284406444</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.9611129868785409</v>
+        <v>0.960663221292599</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.3263860409273997</v>
+        <v>0.3273085310888311</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.9671196433243247</v>
+        <v>0.9697307724154322</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.3915598607890737</v>
+        <v>0.3921298359884779</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.05291608030369088</v>
+        <v>0.05293402055671876</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.05293942460862853</v>
+        <v>0.0528778363302702</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.9205847853908842</v>
+        <v>0.9196453933384029</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.9109288861145952</v>
+        <v>0.9107013709849128</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5674361589637862</v>
+        <v>0.5663063119244335</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.6959495645310151</v>
+        <v>0.7004745353446893</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.4874999999999999</v>
+        <v>0.49125</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.9569894698448002</v>
+        <v>0.959360216120258</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.7097692302368419</v>
+        <v>0.7145455077753315</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.2610399053137851</v>
+        <v>0.2588856807755687</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.2573504130874827</v>
+        <v>0.2551852646401006</v>
       </c>
       <c r="AT9" t="n">
-        <v>233.2883042149124</v>
+        <v>232.3591410223163</v>
       </c>
       <c r="AU9" t="n">
-        <v>145.3409244559601</v>
+        <v>145.6481064162296</v>
       </c>
       <c r="AV9" t="n">
-        <v>223.0322622036826</v>
+        <v>222.2704849331848</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.9742552111706466</v>
+        <v>0.9742029714387206</v>
       </c>
       <c r="AX9" t="n">
-        <v>534.0008882215951</v>
+        <v>533.9722550021582</v>
       </c>
       <c r="AY9" t="n">
-        <v>423.1435900739852</v>
+        <v>423.1322454058821</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.5513218436656993</v>
+        <v>0.5491407084785749</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.5094708402862765</v>
+        <v>0.5079269681456777</v>
       </c>
       <c r="BB9" t="n">
-        <v>571.5617552575151</v>
+        <v>571.1201675926048</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.9567399104829992</v>
+        <v>0.9570016991717233</v>
       </c>
       <c r="BD9" t="n">
-        <v>702.1572925453611</v>
+        <v>702.3494208708123</v>
       </c>
       <c r="BE9" t="n">
-        <v>485.2147361637521</v>
+        <v>485.2811152496905</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.4596568190963038</v>
+        <v>0.4580241801060413</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.4733333333333333</v>
+        <v>0.4773333333333333</v>
       </c>
       <c r="B10" t="n">
-        <v>0.445</v>
+        <v>0.4495</v>
       </c>
       <c r="C10" t="n">
-        <v>1267503.991885038</v>
+        <v>1267617.044000781</v>
       </c>
       <c r="D10" t="n">
         <v>585.270758508015</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7361047036831874</v>
+        <v>0.7360897807656958</v>
       </c>
       <c r="F10" t="n">
-        <v>297.9717233107392</v>
+        <v>296.3184390788605</v>
       </c>
       <c r="G10" t="n">
-        <v>27598.62337277873</v>
+        <v>27078.47357265277</v>
       </c>
       <c r="H10" t="n">
-        <v>25942.705970412</v>
+        <v>25453.76515829361</v>
       </c>
       <c r="I10" t="n">
-        <v>23011.09680701566</v>
+        <v>22581.58273195648</v>
       </c>
       <c r="J10" t="n">
-        <v>24.63568082276857</v>
+        <v>24.17137344472127</v>
       </c>
       <c r="K10" t="n">
-        <v>609.9064393307835</v>
+        <v>609.4421319527362</v>
       </c>
       <c r="L10" t="n">
-        <v>609.9064393307835</v>
+        <v>609.4421319527362</v>
       </c>
       <c r="M10" t="n">
-        <v>1.136889687616665</v>
+        <v>1.134218699348376</v>
       </c>
       <c r="N10" t="n">
-        <v>1441012.217387057</v>
+        <v>1437754.954918399</v>
       </c>
       <c r="O10" t="n">
-        <v>1441012.217387057</v>
+        <v>1437754.954918399</v>
       </c>
       <c r="P10" t="n">
         <v>442.9912926093891</v>
       </c>
       <c r="Q10" t="n">
-        <v>452.2185634265932</v>
+        <v>452.0463989943427</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8780233865861755</v>
+        <v>0.8780171311961088</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2620002940477739</v>
+        <v>0.2633886195120779</v>
       </c>
       <c r="T10" t="n">
-        <v>1.065253300133657</v>
+        <v>1.066578494102191</v>
       </c>
       <c r="U10" t="n">
-        <v>141.0399490337499</v>
+        <v>141.4426682536428</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3639005947591492</v>
+        <v>0.364672484772486</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5428809839569598</v>
+        <v>0.5439021716168616</v>
       </c>
       <c r="X10" t="n">
-        <v>0.05840115876947559</v>
+        <v>0.05824363872918614</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.445</v>
+        <v>0.4495</v>
       </c>
       <c r="Z10" t="n">
-        <v>132.5974168732789</v>
+        <v>133.1951383659478</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.3351370870641959</v>
+        <v>0.3365294725945194</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.5042646819024118</v>
+        <v>0.5061586819210724</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0564549999016528</v>
+        <v>0.0563084564949122</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.9150278007023386</v>
+        <v>0.914283531782479</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.9610954843821731</v>
+        <v>0.9607058272696086</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.3170712219920036</v>
+        <v>0.3181098119961538</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.9517172720336918</v>
+        <v>0.9549232328253213</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.3600326330404789</v>
+        <v>0.3609706113493102</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.05293942460862853</v>
+        <v>0.0528778363302702</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.05391310233810374</v>
+        <v>0.05375127981687648</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.920548238931349</v>
+        <v>0.9197344035641843</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.9195594354841743</v>
+        <v>0.9193614792328587</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5881976314462656</v>
+        <v>0.5869882247301135</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.655154283457094</v>
+        <v>0.6603219259863411</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.4591666666666666</v>
+        <v>0.4634166666666666</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.9456814689742141</v>
+        <v>0.9486043504250566</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.6628199273214817</v>
+        <v>0.6682945721436412</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.2905271855171201</v>
+        <v>0.2882824244387155</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.2888973447122102</v>
+        <v>0.2866286606816801</v>
       </c>
       <c r="AT10" t="n">
-        <v>231.4856566973343</v>
+        <v>230.5988319436543</v>
       </c>
       <c r="AU10" t="n">
-        <v>136.8186829535144</v>
+        <v>137.3189033097953</v>
       </c>
       <c r="AV10" t="n">
-        <v>222.345709564625</v>
+        <v>221.6077990150224</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.9779293928556563</v>
+        <v>0.9778356631416435</v>
       </c>
       <c r="AX10" t="n">
-        <v>572.3534775239125</v>
+        <v>572.2986202630975</v>
       </c>
       <c r="AY10" t="n">
-        <v>438.0754741066519</v>
+        <v>438.0544799157025</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.5284150115214572</v>
+        <v>0.5264158740895194</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.4916775372506739</v>
+        <v>0.4902324175306522</v>
       </c>
       <c r="BB10" t="n">
-        <v>609.9064393307835</v>
+        <v>609.4421319527362</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.9597088665605187</v>
+        <v>0.959945362800342</v>
       </c>
       <c r="BD10" t="n">
-        <v>704.3362276333985</v>
+        <v>704.5097936753625</v>
       </c>
       <c r="BE10" t="n">
-        <v>485.9670123840491</v>
+        <v>486.0268859017463</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.4575325153735128</v>
+        <v>0.4559579015960487</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.445</v>
+        <v>0.4495</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4166666666666666</v>
+        <v>0.4216666666666666</v>
       </c>
       <c r="C11" t="n">
-        <v>1413415.856261558</v>
+        <v>1413541.87064003</v>
       </c>
       <c r="D11" t="n">
         <v>622.4296033215169</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7781177916435859</v>
+        <v>0.7781010033614078</v>
       </c>
       <c r="F11" t="n">
-        <v>297.8082169682268</v>
+        <v>296.1521831628515</v>
       </c>
       <c r="G11" t="n">
-        <v>29018.47580668066</v>
+        <v>28479.74565628555</v>
       </c>
       <c r="H11" t="n">
-        <v>27277.36725827982</v>
+        <v>26770.96091690842</v>
       </c>
       <c r="I11" t="n">
-        <v>24091.09900375148</v>
+        <v>23668.43764046109</v>
       </c>
       <c r="J11" t="n">
-        <v>25.71069838049735</v>
+        <v>25.23337736275803</v>
       </c>
       <c r="K11" t="n">
-        <v>648.1403017020142</v>
+        <v>647.6629806842749</v>
       </c>
       <c r="L11" t="n">
-        <v>648.1403017020142</v>
+        <v>647.6629806842749</v>
       </c>
       <c r="M11" t="n">
-        <v>1.133616272174435</v>
+        <v>1.131168049845624</v>
       </c>
       <c r="N11" t="n">
-        <v>1602271.214007464</v>
+        <v>1598953.401187018</v>
       </c>
       <c r="O11" t="n">
-        <v>1602271.214007464</v>
+        <v>1598953.401187018</v>
       </c>
       <c r="P11" t="n">
         <v>456.837658248206</v>
       </c>
       <c r="Q11" t="n">
-        <v>466.1774803234122</v>
+        <v>466.0057911908793</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8959540439309068</v>
+        <v>0.8959467538397662</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2653834372266647</v>
+        <v>0.2667584227797275</v>
       </c>
       <c r="T11" t="n">
-        <v>1.03305222951582</v>
+        <v>1.03520256682173</v>
       </c>
       <c r="U11" t="n">
-        <v>132.5246565508609</v>
+        <v>133.1204063317017</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3377607721725686</v>
+        <v>0.3388453894983673</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5078315209863722</v>
+        <v>0.5093034843751886</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0588154099561102</v>
+        <v>0.05856522843683203</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4166666666666666</v>
+        <v>0.4216666666666666</v>
       </c>
       <c r="Z11" t="n">
-        <v>124.0867570700945</v>
+        <v>124.8775039003357</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.3099192572990383</v>
+        <v>0.3116102525718044</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.4695482635172004</v>
+        <v>0.4719001526279438</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.05726033254795621</v>
+        <v>0.0569991866427223</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.913758507733758</v>
+        <v>0.9131821038107241</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.9603651810641947</v>
+        <v>0.9600432583058317</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.3081307951746481</v>
+        <v>0.3092356149407436</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.9340401643408068</v>
+        <v>0.9380268380238848</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.3310568450328454</v>
+        <v>0.3323121833376875</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.05391310233810374</v>
+        <v>0.05375127981687648</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.05582121336261999</v>
+        <v>0.05552850503992657</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.9190226123447272</v>
+        <v>0.9183496695904866</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.9281596124975507</v>
+        <v>0.9279950060727989</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.608690873265208</v>
+        <v>0.6074593495418869</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.6145479260868981</v>
+        <v>0.6203334246401707</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.4308333333333333</v>
+        <v>0.4355833333333333</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.9327487297260985</v>
+        <v>0.9363955278546708</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.6159438195232431</v>
+        <v>0.6220825077956035</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.3182008036392003</v>
+        <v>0.3160621032145001</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.3180963448175638</v>
+        <v>0.3159443302282813</v>
       </c>
       <c r="AT11" t="n">
-        <v>229.8424105731522</v>
+        <v>229.0020968160556</v>
       </c>
       <c r="AU11" t="n">
-        <v>128.3057068104777</v>
+        <v>128.9989551160187</v>
       </c>
       <c r="AV11" t="n">
-        <v>222.0862602899936</v>
+        <v>221.3704787375916</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.9809862767968984</v>
+        <v>0.9808639670026166</v>
       </c>
       <c r="AX11" t="n">
-        <v>610.5948991305453</v>
+        <v>610.5187698938081</v>
       </c>
       <c r="AY11" t="n">
-        <v>452.4737226386433</v>
+        <v>452.4455144494128</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.5079685273938219</v>
+        <v>0.5061429266123488</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.4763985170109901</v>
+        <v>0.4750380422781412</v>
       </c>
       <c r="BB11" t="n">
-        <v>648.1403017020142</v>
+        <v>647.6629806842749</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.9621740754982883</v>
+        <v>0.9623898097314252</v>
       </c>
       <c r="BD11" t="n">
-        <v>706.1454596036933</v>
+        <v>706.3037882815179</v>
       </c>
       <c r="BE11" t="n">
-        <v>486.5907650224348</v>
+        <v>486.6453125334641</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.456412813917161</v>
+        <v>0.4548908065817834</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.4166666666666666</v>
+        <v>0.4216666666666666</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3883333333333333</v>
+        <v>0.3938333333333333</v>
       </c>
       <c r="C12" t="n">
-        <v>1559327.720638079</v>
+        <v>1559466.697279278</v>
       </c>
       <c r="D12" t="n">
         <v>659.5884481350188</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8201308796039843</v>
+        <v>0.8201122259571196</v>
       </c>
       <c r="F12" t="n">
-        <v>297.6447106257144</v>
+        <v>295.9859272468424</v>
       </c>
       <c r="G12" t="n">
-        <v>30251.81785252283</v>
+        <v>29710.34632635923</v>
       </c>
       <c r="H12" t="n">
-        <v>28436.70878137146</v>
+        <v>27927.72554677768</v>
       </c>
       <c r="I12" t="n">
-        <v>24870.95465198383</v>
+        <v>24478.00323351468</v>
       </c>
       <c r="J12" t="n">
-        <v>26.59850079231665</v>
+        <v>26.12241929242495</v>
       </c>
       <c r="K12" t="n">
-        <v>686.1869489273354</v>
+        <v>685.7108674274438</v>
       </c>
       <c r="L12" t="n">
-        <v>686.1869489273354</v>
+        <v>685.7108674274438</v>
       </c>
       <c r="M12" t="n">
-        <v>1.128981232540062</v>
+        <v>1.126855772995949</v>
       </c>
       <c r="N12" t="n">
-        <v>1760451.731979864</v>
+        <v>1757294.05062408</v>
       </c>
       <c r="O12" t="n">
-        <v>1760451.731979864</v>
+        <v>1757294.05062408</v>
       </c>
       <c r="P12" t="n">
         <v>470.2765214846174</v>
       </c>
       <c r="Q12" t="n">
-        <v>479.6649705527136</v>
+        <v>479.4985441567283</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9144984034103081</v>
+        <v>0.9144900390830787</v>
       </c>
       <c r="S12" t="n">
-        <v>0.270550115999764</v>
+        <v>0.2718250038327186</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9948990905491514</v>
+        <v>0.9981953315900436</v>
       </c>
       <c r="U12" t="n">
-        <v>124.018629427381</v>
+        <v>124.8073993224185</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3144306746535239</v>
+        <v>0.3157563807972059</v>
       </c>
       <c r="W12" t="n">
-        <v>0.475815371966174</v>
+        <v>0.4776524111349399</v>
       </c>
       <c r="X12" t="n">
-        <v>0.05998092142384246</v>
+        <v>0.05961763500520601</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.3883333333333333</v>
+        <v>0.3938333333333333</v>
       </c>
       <c r="Z12" t="n">
-        <v>115.5853626263191</v>
+        <v>116.5691243473814</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.2873135534964715</v>
+        <v>0.2892419896025067</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.4377919427019134</v>
+        <v>0.4405233864725204</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.05889546038663983</v>
+        <v>0.05849024100115483</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.9111759265774858</v>
+        <v>0.9107999498632829</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.9589323966089885</v>
+        <v>0.958693692884539</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2998312176736487</v>
+        <v>0.300932890494228</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.9133021273714725</v>
+        <v>0.9183243619053558</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.3044385167053856</v>
+        <v>0.3059536774691968</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.05582121336261999</v>
+        <v>0.05552850503992657</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.05873256848713653</v>
+        <v>0.05826439951214323</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.9160254813773016</v>
+        <v>0.915525637845926</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.9367154000096483</v>
+        <v>0.9365918659838088</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.6286751351687813</v>
+        <v>0.6274993351411295</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.5742985310554829</v>
+        <v>0.5806668776409875</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.4025</v>
+        <v>0.4077499999999999</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.9175639214668264</v>
+        <v>0.9221667642386009</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.5694800845231864</v>
+        <v>0.5762356545407744</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.3432653904113435</v>
+        <v>0.3414998865976134</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.3438220428482861</v>
+        <v>0.3420887073645814</v>
       </c>
       <c r="AT12" t="n">
-        <v>228.291845320517</v>
+        <v>227.5092562077241</v>
       </c>
       <c r="AU12" t="n">
-        <v>119.80199602685</v>
+        <v>120.6882618349</v>
       </c>
       <c r="AV12" t="n">
-        <v>222.1870766322743</v>
+        <v>221.4986472018841</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.9835222251394883</v>
+        <v>0.9833829846643083</v>
       </c>
       <c r="AX12" t="n">
-        <v>648.7198981860556</v>
+        <v>648.6280567771141</v>
       </c>
       <c r="AY12" t="n">
-        <v>466.3858722793653</v>
+        <v>466.3528572201165</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.4894913394455699</v>
+        <v>0.4878478874641927</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.4632130555129972</v>
+        <v>0.4619381015878232</v>
       </c>
       <c r="BB12" t="n">
-        <v>686.1869489273354</v>
+        <v>685.7108674274438</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.9642389442003855</v>
+        <v>0.9644355317169063</v>
       </c>
       <c r="BD12" t="n">
-        <v>707.6608794178352</v>
+        <v>707.8051562028172</v>
       </c>
       <c r="BE12" t="n">
-        <v>487.1126079961389</v>
+        <v>487.162261340926</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.4561308268047035</v>
+        <v>0.4546711943412933</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.3883333333333333</v>
+        <v>0.3938333333333333</v>
       </c>
       <c r="B13" t="n">
-        <v>0.36</v>
+        <v>0.366</v>
       </c>
       <c r="C13" t="n">
-        <v>1705239.585014599</v>
+        <v>1705391.523918527</v>
       </c>
       <c r="D13" t="n">
         <v>696.7472929485206</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8621439675643827</v>
+        <v>0.8621234485528316</v>
       </c>
       <c r="F13" t="n">
-        <v>297.4812042832021</v>
+        <v>295.8196713308334</v>
       </c>
       <c r="G13" t="n">
-        <v>31241.88302299291</v>
+        <v>30719.03738497328</v>
       </c>
       <c r="H13" t="n">
-        <v>29367.37004161333</v>
+        <v>28875.89514187488</v>
       </c>
       <c r="I13" t="n">
-        <v>25287.37164263679</v>
+        <v>24951.50377353315</v>
       </c>
       <c r="J13" t="n">
-        <v>27.26055433489986</v>
+        <v>26.80433785417398</v>
       </c>
       <c r="K13" t="n">
-        <v>724.0078472834205</v>
+        <v>723.5516308026945</v>
       </c>
       <c r="L13" t="n">
-        <v>724.0078472834205</v>
+        <v>723.5516308026945</v>
       </c>
       <c r="M13" t="n">
-        <v>1.122963813973579</v>
+        <v>1.121263334583824</v>
       </c>
       <c r="N13" t="n">
-        <v>1914922.348126717</v>
+        <v>1912192.986879876</v>
       </c>
       <c r="O13" t="n">
-        <v>1914922.348126717</v>
+        <v>1912192.986879876</v>
       </c>
       <c r="P13" t="n">
         <v>483.3418741694526</v>
       </c>
       <c r="Q13" t="n">
-        <v>492.706638065828</v>
+        <v>492.5513798662465</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9336198961053839</v>
+        <v>0.933610422109947</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2777419411096173</v>
+        <v>0.2788052258022088</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9499315755816221</v>
+        <v>0.9547700581940284</v>
       </c>
       <c r="U13" t="n">
-        <v>115.5218676633101</v>
+        <v>116.5036472257932</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2938451896376161</v>
+        <v>0.2953239517243477</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4470267751871176</v>
+        <v>0.4491109583226507</v>
       </c>
       <c r="X13" t="n">
-        <v>0.06187122459721857</v>
+        <v>0.06136696819260479</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.36</v>
+        <v>0.366</v>
       </c>
       <c r="Z13" t="n">
-        <v>107.0932335419527</v>
+        <v>108.269999707085</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2672282846819579</v>
+        <v>0.2693209680835347</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.4091059358646851</v>
+        <v>0.4121144803622692</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.06136979849785384</v>
+        <v>0.06077989459910128</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.9072538864515785</v>
+        <v>0.907129750913281</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.9567421501336806</v>
+        <v>0.9566124246331672</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.2924939941202897</v>
+        <v>0.2934993946135828</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.8884898210558309</v>
+        <v>0.8948912786102198</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.2800557892516001</v>
+        <v>0.2817626701603202</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.05873256848713653</v>
+        <v>0.05826439951214323</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.05981583621346994</v>
+        <v>0.05921684165741564</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.9114335322363536</v>
+        <v>0.9111611613348617</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.9451810231195322</v>
+        <v>0.9451114233715572</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.6478554829422551</v>
+        <v>0.6468369132009922</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.534576875262367</v>
+        <v>0.5414858336198617</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.3741666666666666</v>
+        <v>0.3799166666666667</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.8993359353138319</v>
+        <v>0.9052038622295482</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.5237459361863152</v>
+        <v>0.5310626589094749</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.364759060051465</v>
+        <v>0.3637180286096865</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.3647438848695157</v>
+        <v>0.3638286197007449</v>
       </c>
       <c r="AT13" t="n">
-        <v>226.7459949749261</v>
+        <v>226.0407913801597</v>
       </c>
       <c r="AU13" t="n">
-        <v>111.3075506026314</v>
+        <v>112.3868234664391</v>
       </c>
       <c r="AV13" t="n">
-        <v>222.5583757965641</v>
+        <v>221.9110278634661</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.9856091674211389</v>
+        <v>0.9854639605896526</v>
       </c>
       <c r="AX13" t="n">
-        <v>686.7205193059237</v>
+        <v>686.619346839168</v>
       </c>
       <c r="AY13" t="n">
-        <v>479.8514250507924</v>
+        <v>479.8160762158486</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.4725337534444646</v>
+        <v>0.4710988284570808</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.451705657285724</v>
+        <v>0.450533765479911</v>
       </c>
       <c r="BB13" t="n">
-        <v>724.0078472834205</v>
+        <v>723.5516308026945</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.9659936665293454</v>
+        <v>0.9661698876937488</v>
       </c>
       <c r="BD13" t="n">
-        <v>708.9486809051269</v>
+        <v>709.0780106992862</v>
       </c>
       <c r="BE13" t="n">
-        <v>487.5556303720521</v>
+        <v>487.6000994539179</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.4564779113036406</v>
+        <v>0.455108659969497</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.36</v>
+        <v>0.366</v>
       </c>
       <c r="B14" t="n">
-        <v>0.36</v>
+        <v>0.366</v>
       </c>
       <c r="C14" t="n">
-        <v>1851151.44939112</v>
+        <v>1851316.350557775</v>
       </c>
       <c r="D14" t="n">
         <v>733.9061377620225</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9041570555247811</v>
+        <v>0.9041346711485436</v>
       </c>
       <c r="F14" t="n">
-        <v>297.3176979406897</v>
+        <v>295.6534154148244</v>
       </c>
       <c r="G14" t="n">
-        <v>31920.53078366392</v>
+        <v>31444.23444505393</v>
       </c>
       <c r="H14" t="n">
-        <v>30005.29893664408</v>
+        <v>29557.58037835069</v>
       </c>
       <c r="I14" t="n">
-        <v>25276.49276923406</v>
+        <v>25029.11638499706</v>
       </c>
       <c r="J14" t="n">
-        <v>27.60028025904358</v>
+        <v>27.18844774532111</v>
       </c>
       <c r="K14" t="n">
-        <v>761.506418021066</v>
+        <v>761.0945855073436</v>
       </c>
       <c r="L14" t="n">
-        <v>761.506418021066</v>
+        <v>761.0945855073436</v>
       </c>
       <c r="M14" t="n">
-        <v>1.115342510425823</v>
+        <v>1.11416977193039</v>
       </c>
       <c r="N14" t="n">
-        <v>2064667.904742293</v>
+        <v>2062680.716071959</v>
       </c>
       <c r="O14" t="n">
-        <v>2064667.904742293</v>
+        <v>2062680.716071959</v>
       </c>
       <c r="P14" t="n">
         <v>496.0632298322525</v>
       </c>
       <c r="Q14" t="n">
-        <v>505.3049593685614</v>
+        <v>505.1683031630274</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9532837932785919</v>
+        <v>0.95327317794347</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2872434660618717</v>
+        <v>0.2879557252140741</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8973380909601371</v>
+        <v>0.9041782148066957</v>
       </c>
       <c r="U14" t="n">
-        <v>107.0343712586483</v>
+        <v>108.2091500418257</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2760343168877671</v>
+        <v>0.2775556733353156</v>
       </c>
       <c r="W14" t="n">
-        <v>0.4217353077120997</v>
+        <v>0.4239089826554646</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0645173323473172</v>
+        <v>0.06383389823301641</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.36</v>
+        <v>0.366</v>
       </c>
       <c r="Z14" t="n">
-        <v>107.0343712586483</v>
+        <v>108.2091500418257</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.2709858121143243</v>
+        <v>0.2725530539245822</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.414504721461969</v>
+        <v>0.4167522097442211</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.05995082316390905</v>
+        <v>0.05934631531060342</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.9095051536696753</v>
+        <v>0.909429439730491</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.9559259141562177</v>
+        <v>0.9558868129828687</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.2890170234821871</v>
+        <v>0.2897096758504782</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.8943351561349819</v>
+        <v>0.9012251125583335</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.2716378904005688</v>
+        <v>0.2731889702002319</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.05981583621346994</v>
+        <v>0.05921684165741564</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.05981583621346994</v>
+        <v>0.05921684165741564</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.9097190262442579</v>
+        <v>0.9096368497752779</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.9546048537174048</v>
+        <v>0.9545799954631693</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.6651186060212817</v>
+        <v>0.6644066348749251</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.4955263450974872</v>
+        <v>0.5029302170208082</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.36</v>
+        <v>0.366</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.8935430921286539</v>
+        <v>0.9004467114969256</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.4961058456546084</v>
+        <v>0.5035089684840817</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.3980167470311667</v>
+        <v>0.3975164944761174</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.3982293104803735</v>
+        <v>0.3977161440742518</v>
       </c>
       <c r="AT14" t="n">
-        <v>225.1010566548027</v>
+        <v>224.5026475751386</v>
       </c>
       <c r="AU14" t="n">
-        <v>107.0343712586483</v>
+        <v>108.2091500418257</v>
       </c>
       <c r="AV14" t="n">
-        <v>224.8600127977224</v>
+        <v>224.2667433906221</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.9873008426500506</v>
+        <v>0.9871604746998967</v>
       </c>
       <c r="AX14" t="n">
-        <v>724.5861482384889</v>
+        <v>724.4831313383258</v>
       </c>
       <c r="AY14" t="n">
-        <v>492.9033733951974</v>
+        <v>492.8683332673551</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.4566839441659134</v>
+        <v>0.4555022760071658</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.4449986263319318</v>
+        <v>0.4439446061568256</v>
       </c>
       <c r="BB14" t="n">
-        <v>761.506418021066</v>
+        <v>761.0945855073436</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.9669960370937822</v>
+        <v>0.9671521977773768</v>
       </c>
       <c r="BD14" t="n">
-        <v>709.6843268146791</v>
+        <v>709.7989340988463</v>
       </c>
       <c r="BE14" t="n">
-        <v>487.808522661261</v>
+        <v>487.8479092948367</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.4609595821962861</v>
+        <v>0.4597062713967353</v>
       </c>
     </row>
   </sheetData>
